--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N25_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.76535228871097</v>
+        <v>6.624369746915533</v>
       </c>
       <c r="D2" t="n">
-        <v>40.58819135801233</v>
+        <v>6.595581095677004</v>
       </c>
       <c r="E2" t="n">
-        <v>13.85951445374701</v>
+        <v>2.252171098733889</v>
       </c>
       <c r="F2" t="n">
-        <v>16.17029272386381</v>
+        <v>2.627672567627869</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.472031303215263</v>
+        <v>0.5642050867724803</v>
       </c>
       <c r="D3" t="n">
-        <v>5.307733717159135</v>
+        <v>0.8625067290383596</v>
       </c>
       <c r="E3" t="n">
-        <v>13.85951445374701</v>
+        <v>2.252171098733889</v>
       </c>
       <c r="F3" t="n">
-        <v>16.17029272386381</v>
+        <v>2.627672567627869</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.15571618878294</v>
+        <v>3.600303880677227</v>
       </c>
       <c r="D4" t="n">
-        <v>22.01740107944437</v>
+        <v>3.57782767540971</v>
       </c>
       <c r="E4" t="n">
-        <v>13.85951445374701</v>
+        <v>2.252171098733889</v>
       </c>
       <c r="F4" t="n">
-        <v>16.17029272386381</v>
+        <v>2.627672567627869</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>11.49025650225083</v>
+        <v>1.867166681615759</v>
       </c>
       <c r="D5" t="n">
-        <v>3.354101966249685</v>
+        <v>0.5450415695155738</v>
       </c>
       <c r="E5" t="n">
-        <v>13.85951445374701</v>
+        <v>2.252171098733889</v>
       </c>
       <c r="F5" t="n">
-        <v>16.17029272386381</v>
+        <v>2.627672567627869</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.92269909816674</v>
+        <v>2.912438603452095</v>
       </c>
       <c r="D6" t="n">
-        <v>6.519629957208556</v>
+        <v>1.05943986804639</v>
       </c>
       <c r="E6" t="n">
-        <v>13.85951445374701</v>
+        <v>2.252171098733889</v>
       </c>
       <c r="F6" t="n">
-        <v>16.17029272386381</v>
+        <v>2.627672567627869</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.91483155261128</v>
+        <v>7.136160127299332</v>
       </c>
       <c r="D7" t="n">
-        <v>33.76072051489807</v>
+        <v>5.486117083670936</v>
       </c>
       <c r="E7" t="n">
-        <v>13.85951445374701</v>
+        <v>2.252171098733889</v>
       </c>
       <c r="F7" t="n">
-        <v>16.17029272386381</v>
+        <v>2.627672567627869</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>18.54630200235957</v>
+        <v>3.01377407538343</v>
       </c>
       <c r="D8" t="n">
-        <v>29.97244227341812</v>
+        <v>4.870521869430445</v>
       </c>
       <c r="E8" t="n">
-        <v>13.85951445374701</v>
+        <v>2.252171098733889</v>
       </c>
       <c r="F8" t="n">
-        <v>16.17029272386381</v>
+        <v>2.627672567627869</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>12.43219453240645</v>
+        <v>2.020231611516048</v>
       </c>
       <c r="D9" t="n">
-        <v>12.18744785320957</v>
+        <v>1.980460276146556</v>
       </c>
       <c r="E9" t="n">
-        <v>13.85951445374701</v>
+        <v>2.252171098733889</v>
       </c>
       <c r="F9" t="n">
-        <v>16.17029272386381</v>
+        <v>2.627672567627869</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>43.30803266686544</v>
+        <v>7.037555308365634</v>
       </c>
       <c r="D10" t="n">
-        <v>36.39137174484643</v>
+        <v>5.913597908537545</v>
       </c>
       <c r="E10" t="n">
-        <v>13.85951445374701</v>
+        <v>2.252171098733889</v>
       </c>
       <c r="F10" t="n">
-        <v>16.17029272386381</v>
+        <v>2.627672567627869</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>31.02182047484776</v>
+        <v>5.041045827162762</v>
       </c>
       <c r="D11" t="n">
-        <v>49.16476469629703</v>
+        <v>7.989274263148268</v>
       </c>
       <c r="E11" t="n">
-        <v>13.85951445374701</v>
+        <v>2.252171098733889</v>
       </c>
       <c r="F11" t="n">
-        <v>16.17029272386381</v>
+        <v>2.627672567627869</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>25.83015684182889</v>
+        <v>4.197400486797195</v>
       </c>
       <c r="D12" t="n">
-        <v>51.80218771899085</v>
+        <v>8.417855504336014</v>
       </c>
       <c r="E12" t="n">
-        <v>13.85951445374701</v>
+        <v>2.252171098733889</v>
       </c>
       <c r="F12" t="n">
-        <v>16.17029272386381</v>
+        <v>2.627672567627869</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>46.14046344451852</v>
+        <v>7.49782530973426</v>
       </c>
       <c r="D13" t="n">
-        <v>22.58471769510476</v>
+        <v>3.670016625454524</v>
       </c>
       <c r="E13" t="n">
-        <v>13.85951445374701</v>
+        <v>2.252171098733889</v>
       </c>
       <c r="F13" t="n">
-        <v>16.17029272386381</v>
+        <v>2.627672567627869</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
